--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -426,19 +426,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4225352112676056</v>
+        <v>0.4084507042253521</v>
       </c>
       <c r="D2">
-        <v>0.5985401459854015</v>
+        <v>0.6043165467625899</v>
       </c>
       <c r="E2">
         <v>135</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
